--- a/temp_documents/Attestation_Collective_ConcoursMathmatiques_17.xlsx
+++ b/temp_documents/Attestation_Collective_ConcoursMathmatiques_17.xlsx
@@ -15,21 +15,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="27">
-  <si>
-    <t xml:space="preserve">REPUBLIQUE DU BENIN </t>
-  </si>
-  <si>
-    <t>MINISTERE DE L'ECONOMIE ET DES FINANCES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIRECTION DES AFFAIRES ETRANGERES </t>
-  </si>
-  <si>
-    <t>SERVICE DES DROITS ET AFFAIRES</t>
-  </si>
-  <si>
-    <t>PORTO, LE 2025-07-21</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
+  <si>
+    <t>RÉPUBLIQUE DU BÉNIN</t>
+  </si>
+  <si>
+    <t>MINISTÈRE DE L'ÉCONOMIE ET DES FINANCES</t>
+  </si>
+  <si>
+    <t>DIRECTION GÉNÉRALE DU TRÉSOR ET DE LA COMPTABILITÉ PUBLIQUE</t>
+  </si>
+  <si>
+    <t>Direction des Affaires Administratives et Financières</t>
+  </si>
+  <si>
+    <t>Service du Personnel et des Moyens</t>
+  </si>
+  <si>
+    <t>PORTO, LE 2025-07-22</t>
   </si>
   <si>
     <t>ATTESTATION COLLECTIVE DE TRAVAIL</t>
@@ -71,16 +74,46 @@
     <t>Numéro de Compte</t>
   </si>
   <si>
+    <t>ABLET Janvier</t>
+  </si>
+  <si>
+    <t>Controleur</t>
+  </si>
+  <si>
+    <t>UBA</t>
+  </si>
+  <si>
+    <t>UB123654789</t>
+  </si>
+  <si>
+    <t>NSIA</t>
+  </si>
+  <si>
+    <t>NS0000000012365</t>
+  </si>
+  <si>
     <t>AHOSSOU Kévin</t>
   </si>
   <si>
     <t>Superviseur</t>
   </si>
   <si>
-    <t>UBA</t>
-  </si>
-  <si>
     <t>UA123654789</t>
+  </si>
+  <si>
+    <t>EZIN Yannick</t>
+  </si>
+  <si>
+    <t>ECOBANK</t>
+  </si>
+  <si>
+    <t>EC123654</t>
+  </si>
+  <si>
+    <t>UB123654</t>
+  </si>
+  <si>
+    <t>NS123654</t>
   </si>
   <si>
     <t>L'ORGANISATEUR</t>
@@ -554,7 +587,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="true" style="0"/>
@@ -569,88 +602,84 @@
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -658,40 +687,125 @@
         <v>1</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="8">
+        <v>2</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="D18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="8">
+        <v>3</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>25</v>
+      <c r="E19" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="8">
+        <v>4</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="8">
+        <v>5</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="8">
+        <v>6</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>26</v>
+      <c r="E22" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -701,8 +815,6 @@
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A9:E9"/>
@@ -712,12 +824,12 @@
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D28:E28"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
